--- a/sections/05-invoice-button/01-copy-template/book/invoice.xlsx
+++ b/sections/05-invoice-button/01-copy-template/book/invoice.xlsx
@@ -1390,7 +1390,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdButtons"/>
 </worksheet>
 </file>
 
